--- a/output/pdf_financials_xlsx/SUM.xlsx
+++ b/output/pdf_financials_xlsx/SUM.xlsx
@@ -3774,7 +3774,11 @@
           <t>General and administration expenses 9,12</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>-0.082037</v>
       </c>

--- a/output/pdf_financials_xlsx/SUM.xlsx
+++ b/output/pdf_financials_xlsx/SUM.xlsx
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000932</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.313091</v>
       </c>
     </row>
     <row r="102">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.07191</v>
+        <v>0.070978</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.322063</v>
+        <v>0.008972000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -3224,7 +3224,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>-0.000932</v>
       </c>
